--- a/api/src/main/resources/importaciones/rrhh-parametros.xlsx
+++ b/api/src/main/resources/importaciones/rrhh-parametros.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismael\Documents\Software Ecuador\src\main\resources\importaciones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismael\Documents\calero-app-desktop\api\src\main\resources\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0474EF0-5CDF-46D1-B42C-CCFE7131E3A3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8DDC81-DA1E-4F0A-8BD9-4B781959CD86}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>AÑO</t>
   </si>
@@ -61,10 +61,13 @@
     <t>Retenido y asumido otros empleadores  (Anual)</t>
   </si>
   <si>
-    <t>0902274026</t>
-  </si>
-  <si>
     <t>Número cargas familiares (2026)</t>
+  </si>
+  <si>
+    <t>1751136138001</t>
+  </si>
+  <si>
+    <t>1768143140001</t>
   </si>
 </sst>
 </file>
@@ -581,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -622,7 +625,7 @@
         <v>2026</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="8">
         <v>5</v>
@@ -678,21 +681,50 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
+    <row r="4" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="8">
+        <v>5</v>
+      </c>
+      <c r="D4" s="7">
+        <v>200</v>
+      </c>
+      <c r="E4" s="7">
+        <v>300</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7">
+        <v>200</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7">
+        <v>0</v>
+      </c>
+      <c r="N4" s="7">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
